--- a/cases/Case_14bus_v1/pf_info_extendedCase_14bus_v1.xlsx
+++ b/cases/Case_14bus_v1/pf_info_extendedCase_14bus_v1.xlsx
@@ -555,10 +555,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.084110368882355</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-0.2403043493698371</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -578,10 +578,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.3999998928009251</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.4292003924046128</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>0.39999999684367</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1797864329175196</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -624,10 +624,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>-6.738144930906742E-08</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-6.73415111174247E-08</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -647,10 +647,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1.973857093051645E-08</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4.668490126424896E-08</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -670,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.3000000124874319</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.7199130769011608</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>7.556640146955118E-09</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2.101644369645328E-08</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -716,10 +716,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.3500000085256443</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.1998208061012816</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>-1.602908422659866E-08</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-5.855625798134589E-08</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -762,10 +762,10 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.2000000102226739</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>6.625920430380905E-09</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.02499999916666637</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>-1.203750672057469E-09</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -808,10 +808,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.02499999951969883</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>-3.40011709065724E-09</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -831,10 +831,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.09999996114127119</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>-3.62244942375689E-08</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.1290590214910489</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>-1.204380611907752E-08</v>
       </c>
     </row>
     <row r="16" spans="1:7">
